--- a/artfynd/A 26389-2019 artfynd.xlsx
+++ b/artfynd/A 26389-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121183275</v>
       </c>
       <c r="B2" t="n">
-        <v>58204</v>
+        <v>58207</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bettina Ekdahl, Marcus Törnberg</t>
+          <t>Marcus Törnberg, Bettina Ekdahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 26389-2019 artfynd.xlsx
+++ b/artfynd/A 26389-2019 artfynd.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marcus Törnberg, Bettina Ekdahl</t>
+          <t>Bettina Ekdahl, Marcus Törnberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 26389-2019 artfynd.xlsx
+++ b/artfynd/A 26389-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121183275</v>
       </c>
       <c r="B2" t="n">
-        <v>58207</v>
+        <v>58210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 26389-2019 artfynd.xlsx
+++ b/artfynd/A 26389-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121183275</v>
       </c>
       <c r="B2" t="n">
-        <v>58210</v>
+        <v>58211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
